--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVIII/LTAIPT_A63F28A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVIII/LTAIPT_A63F28A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -17,30 +17,40 @@
     <sheet name="Hidden_7" sheetId="8" r:id="rId8"/>
     <sheet name="Hidden_8" sheetId="9" r:id="rId9"/>
     <sheet name="Hidden_9" sheetId="10" r:id="rId10"/>
-    <sheet name="Tabla_436444" sheetId="11" r:id="rId11"/>
-    <sheet name="Tabla_436473" sheetId="12" r:id="rId12"/>
-    <sheet name="Tabla_436474" sheetId="13" r:id="rId13"/>
-    <sheet name="Tabla_436475" sheetId="14" r:id="rId14"/>
-    <sheet name="Tabla_436476" sheetId="15" r:id="rId15"/>
-    <sheet name="Tabla_436477" sheetId="16" r:id="rId16"/>
+    <sheet name="Hidden_10" sheetId="11" r:id="rId11"/>
+    <sheet name="Tabla_436444" sheetId="12" r:id="rId12"/>
+    <sheet name="Hidden_1_Tabla_436444" sheetId="13" r:id="rId13"/>
+    <sheet name="Tabla_436473" sheetId="14" r:id="rId14"/>
+    <sheet name="Hidden_1_Tabla_436473" sheetId="15" r:id="rId15"/>
+    <sheet name="Tabla_436474" sheetId="16" r:id="rId16"/>
+    <sheet name="Hidden_1_Tabla_436474" sheetId="17" r:id="rId17"/>
+    <sheet name="Tabla_436475" sheetId="18" r:id="rId18"/>
+    <sheet name="Hidden_1_Tabla_436475" sheetId="19" r:id="rId19"/>
+    <sheet name="Tabla_436476" sheetId="20" r:id="rId20"/>
+    <sheet name="Tabla_436477" sheetId="21" r:id="rId21"/>
   </sheets>
   <definedNames>
+    <definedName name="Hidden_1_Tabla_4364446">Hidden_1_Tabla_436444!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4364736">Hidden_1_Tabla_436473!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4364746">Hidden_1_Tabla_436474!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1_Tabla_4364755">Hidden_1_Tabla_436475!$A$1:$A$2</definedName>
+    <definedName name="Hidden_1071">Hidden_10!$A$1:$A$2</definedName>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$3</definedName>
     <definedName name="Hidden_25">Hidden_2!$A$1:$A$5</definedName>
     <definedName name="Hidden_36">Hidden_3!$A$1:$A$2</definedName>
-    <definedName name="Hidden_424">Hidden_4!$A$1:$A$26</definedName>
-    <definedName name="Hidden_528">Hidden_5!$A$1:$A$41</definedName>
-    <definedName name="Hidden_635">Hidden_6!$A$1:$A$32</definedName>
-    <definedName name="Hidden_762">Hidden_7!$A$1:$A$3</definedName>
-    <definedName name="Hidden_869">Hidden_8!$A$1:$A$3</definedName>
-    <definedName name="Hidden_970">Hidden_9!$A$1:$A$2</definedName>
+    <definedName name="Hidden_423">Hidden_4!$A$1:$A$2</definedName>
+    <definedName name="Hidden_525">Hidden_5!$A$1:$A$26</definedName>
+    <definedName name="Hidden_629">Hidden_6!$A$1:$A$41</definedName>
+    <definedName name="Hidden_736">Hidden_7!$A$1:$A$32</definedName>
+    <definedName name="Hidden_863">Hidden_8!$A$1:$A$3</definedName>
+    <definedName name="Hidden_970">Hidden_9!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="383">
   <si>
     <t>48983</t>
   </si>
@@ -151,6 +161,9 @@
   </si>
   <si>
     <t>436484</t>
+  </si>
+  <si>
+    <t>571936</t>
   </si>
   <si>
     <t>436491</t>
@@ -400,6 +413,9 @@
     <t>Razón social del contratista o proveedor</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFC de la persona física o moral contratista o proveedor </t>
   </si>
   <si>
@@ -576,460 +592,451 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4820414</t>
+    <t>6227604</t>
   </si>
   <si>
     <t>ver nota</t>
   </si>
   <si>
-    <t>4820413</t>
-  </si>
-  <si>
-    <t>4534586</t>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>6227605</t>
+  </si>
+  <si>
+    <t>DD8DF0569FF9985DE745D24A67351140</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>8145163</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>subdirección financiera</t>
+  </si>
+  <si>
+    <t>05/07/2023</t>
+  </si>
+  <si>
+    <t>DERIVADO DEL CIERRE DEL SEGUNDO TRIMESTRE DEL AÑO 2023 (ABRIL, MAYO Y JUNIO), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE LICITACIÓN PÚBLICA TODA VEZ QUE COMO LO MENCIONA EL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO: “ARTÍCULO 42. LAS DEPENDENCIAS Y ENTIDADES, BAJO SU RESPONSABILIDAD, PODRÁN CONTRATAR ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS, SIN SUJETARSE AL PROCEDIMIENTO DE LICITACIÓN PÚBLICA, A TRAVÉS DE LOS DE INVITACIÓN A CUANDO MENOS TRES PERSONAS O DE ADJUDICACIÓN DIRECTA, CUANDO EL IMPORTE DE CADA OPERACIÓN NO EXCEDA LOS MONTOS MÁXIMOS QUE AL EFECTO SE ESTABLECERÁN EN EL PRESUPUESTO DE EGRESOS DE LA FEDERACIÓN, SIEMPRE QUE LAS OPERACIONES NO SE FRACCIONEN PARA QUEDAR COMPRENDIDAS EN LOS SUPUESTOS DE EXCEPCIÓN A LA LICITACIÓN PÚBLICA A QUE SE REFIERE ESTE ARTÍCULO. SI EL MONTO DE LA OPERACIÓN CORRESPONDE A UNA INVITACIÓN A CUANDO MENOS TRES PERSONAS, LA PROCEDENCIA DE LA ADJUDICACIÓN DIRECTA SÓLO PODRÁ SER AUTORIZADA POR EL OFICIAL MAYOR O EQUIVALENTE.”…</t>
+  </si>
+  <si>
+    <t>5C969468A5A5ED89620286B5BC2CB530</t>
+  </si>
+  <si>
+    <t>8145164</t>
+  </si>
+  <si>
+    <t>Licitación pública</t>
+  </si>
+  <si>
+    <t>Invitación a cuando menos tres personas</t>
+  </si>
+  <si>
+    <t>Otro (especificar)</t>
+  </si>
+  <si>
+    <t>Obra pública</t>
+  </si>
+  <si>
+    <t>Servicios relacionados con obra pública</t>
+  </si>
+  <si>
+    <t>Adquisiciones</t>
+  </si>
+  <si>
+    <t>Arrendamientos</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Nacional</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Carretera</t>
+  </si>
+  <si>
+    <t>Privada</t>
+  </si>
+  <si>
+    <t>Eje vial</t>
+  </si>
+  <si>
+    <t>Circunvalación</t>
+  </si>
+  <si>
+    <t>Brecha</t>
+  </si>
+  <si>
+    <t>Diagonal</t>
+  </si>
+  <si>
+    <t>Calle</t>
+  </si>
+  <si>
+    <t>Corredor</t>
+  </si>
+  <si>
+    <t>Circuito</t>
+  </si>
+  <si>
+    <t>Pasaje</t>
+  </si>
+  <si>
+    <t>Vereda</t>
+  </si>
+  <si>
+    <t>Calzada</t>
+  </si>
+  <si>
+    <t>Viaducto</t>
+  </si>
+  <si>
+    <t>Prolongación</t>
+  </si>
+  <si>
+    <t>Boulevard</t>
+  </si>
+  <si>
+    <t>Peatonal</t>
+  </si>
+  <si>
+    <t>Retorno</t>
+  </si>
+  <si>
+    <t>Camino</t>
+  </si>
+  <si>
+    <t>Callejón</t>
+  </si>
+  <si>
+    <t>Cerrada</t>
+  </si>
+  <si>
+    <t>Ampliación</t>
+  </si>
+  <si>
+    <t>Continuación</t>
+  </si>
+  <si>
+    <t>Terracería</t>
+  </si>
+  <si>
+    <t>Andador</t>
+  </si>
+  <si>
+    <t>Periférico</t>
+  </si>
+  <si>
+    <t>Avenida</t>
+  </si>
+  <si>
+    <t>Aeropuerto</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>Cantón</t>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Ciudad industrial</t>
+  </si>
+  <si>
+    <t>Colonia</t>
+  </si>
+  <si>
+    <t>Condominio</t>
+  </si>
+  <si>
+    <t>Conjunto habitacional</t>
+  </si>
+  <si>
+    <t>Corredor industrial</t>
+  </si>
+  <si>
+    <t>Coto</t>
+  </si>
+  <si>
+    <t>Cuartel</t>
+  </si>
+  <si>
+    <t>Ejido</t>
+  </si>
+  <si>
+    <t>Exhacienda</t>
+  </si>
+  <si>
+    <t>Fracción</t>
+  </si>
+  <si>
+    <t>Fraccionamiento</t>
+  </si>
+  <si>
+    <t>Granja</t>
+  </si>
+  <si>
+    <t>Hacienda</t>
+  </si>
+  <si>
+    <t>Ingenio</t>
+  </si>
+  <si>
+    <t>Manzana</t>
+  </si>
+  <si>
+    <t>Paraje</t>
+  </si>
+  <si>
+    <t>Parque industrial</t>
+  </si>
+  <si>
+    <t>Pueblo</t>
+  </si>
+  <si>
+    <t>Puerto</t>
+  </si>
+  <si>
+    <t>Ranchería</t>
+  </si>
+  <si>
+    <t>Rancho</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Residencial</t>
+  </si>
+  <si>
+    <t>Rinconada</t>
+  </si>
+  <si>
+    <t>Sección</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Supermanzana</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>Unidad habitacional</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>Zona federal</t>
+  </si>
+  <si>
+    <t>Zona industrial</t>
+  </si>
+  <si>
+    <t>Zona militar</t>
+  </si>
+  <si>
+    <t>Zona naval</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Guerrero</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>Quintana Roo</t>
+  </si>
+  <si>
+    <t>Guanajuato</t>
+  </si>
+  <si>
+    <t>Durango</t>
+  </si>
+  <si>
+    <t>Michoacán de Ocampo</t>
+  </si>
+  <si>
+    <t>San Luis Potosí</t>
+  </si>
+  <si>
+    <t>Campeche</t>
+  </si>
+  <si>
+    <t>Coahuila de Zaragoza</t>
+  </si>
+  <si>
+    <t>Nayarit</t>
+  </si>
+  <si>
+    <t>Zacatecas</t>
+  </si>
+  <si>
+    <t>Morelos</t>
+  </si>
+  <si>
+    <t>Sonora</t>
+  </si>
+  <si>
+    <t>Baja California Sur</t>
+  </si>
+  <si>
+    <t>Colima</t>
+  </si>
+  <si>
+    <t>Tabasco</t>
+  </si>
+  <si>
+    <t>Oaxaca</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>Jalisco</t>
+  </si>
+  <si>
+    <t>Chiapas</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>Aguascalientes</t>
+  </si>
+  <si>
+    <t>Tamaulipas</t>
+  </si>
+  <si>
+    <t>Sinaloa</t>
+  </si>
+  <si>
+    <t>Yucatán</t>
+  </si>
+  <si>
+    <t>Chihuahua</t>
+  </si>
+  <si>
+    <t>Querétaro</t>
+  </si>
+  <si>
+    <t>Nuevo León</t>
+  </si>
+  <si>
+    <t>Veracruz de Ignacio de la Llave</t>
+  </si>
+  <si>
+    <t>Ciudad de México</t>
+  </si>
+  <si>
+    <t>Baja California</t>
+  </si>
+  <si>
+    <t>Federales</t>
+  </si>
+  <si>
+    <t>Estatales</t>
+  </si>
+  <si>
+    <t>Municipales</t>
+  </si>
+  <si>
+    <t>En planeación</t>
+  </si>
+  <si>
+    <t>En ejecución</t>
+  </si>
+  <si>
+    <t>En finiquito</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>56475</t>
+  </si>
+  <si>
+    <t>56476</t>
+  </si>
+  <si>
+    <t>56477</t>
+  </si>
+  <si>
+    <t>56478</t>
+  </si>
+  <si>
+    <t>77803</t>
+  </si>
+  <si>
+    <t>56479</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Nombre(s)</t>
+  </si>
+  <si>
+    <t>Primer apellido</t>
+  </si>
+  <si>
+    <t>Segundo apellido</t>
+  </si>
+  <si>
+    <t>Razón Social</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFC de los posibles contratantes </t>
+  </si>
+  <si>
+    <t>AE57B1F2A7057647699CCC19BF4A55CF</t>
   </si>
   <si>
     <t>VER NOTA</t>
   </si>
   <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>4534585</t>
-  </si>
-  <si>
-    <t>A5B041CFFF077E3585FBBCB15F84F869</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>3087365</t>
-  </si>
-  <si>
-    <t>05/07/2022</t>
-  </si>
-  <si>
-    <t>DERIVADO DEL CIERRE DEL SEGUNDO TRIMESTRE DEL AÑO 2022 (ABRIL. MAYO. JUNIO), EL COLEGIO DE BACHILLERES DEL ESTADO DE TLAXCALA, NO  REALIZO ANTE LA DIRECCIÓN GENERAL DE RECURSOS MATERIALES, SERVICIOS Y ADQUISICIONES DEL ESTADO DE TLAXCALA, PROCEDIMIENTO DE ADQUISICIONES MEDIANTE LICITACIÓN PÚBLICA TODA VEZ QUE COMO LO MENCIONA EL ARTÍCULO 42 DE LA LEY DE ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS DEL SECTOR PÚBLICO: “ARTÍCULO 42. LAS DEPENDENCIAS Y ENTIDADES, BAJO SU RESPONSABILIDAD, PODRÁN CONTRATAR ADQUISICIONES, ARRENDAMIENTOS Y SERVICIOS, SIN SUJETARSE AL PROCEDIMIENTO DE LICITACIÓN PÚBLICA, A TRAVÉS DE LOS DE INVITACIÓN A CUANDO MENOS TRES PERSONAS O DE ADJUDICACIÓN DIRECTA, CUANDO EL IMPORTE DE CADA OPERACIÓN NO EXCEDA LOS MONTOS MÁXIMOS QUE AL EFECTO SE ESTABLECERÁN EN EL PRESUPUESTO DE EGRESOS DE LA FEDERACIÓN, SIEMPRE QUE LAS OPERACIONES NO SE FRACCIONEN PARA QUEDAR COMPRENDIDAS EN LOS SUPUESTOS DE EXCEPCIÓN A LA LICITACIÓN PÚBLICA A QUE SE REFIERE ESTE ARTÍCULO. SI EL MONTO DE LA OPERACIÓN CORRESPONDE A UNA INVITACIÓN A CUANDO MENOS TRES PERSONAS, LA PROCEDENCIA DE LA ADJUDICACIÓN DIRECTA SÓLO PODRÁ SER AUTORIZADA POR EL OFICIAL MAYOR O EQUIVALENTE.”…</t>
-  </si>
-  <si>
-    <t>0417FB00423558FB933399B4EE116DAA</t>
-  </si>
-  <si>
-    <t>3087366</t>
-  </si>
-  <si>
-    <t>2623616</t>
-  </si>
-  <si>
-    <t>2623615</t>
-  </si>
-  <si>
-    <t>Licitación pública</t>
-  </si>
-  <si>
-    <t>Invitación a cuando menos tres personas</t>
-  </si>
-  <si>
-    <t>Otro (especificar)</t>
-  </si>
-  <si>
-    <t>Obra pública</t>
-  </si>
-  <si>
-    <t>Servicios relacionados con obra pública</t>
-  </si>
-  <si>
-    <t>Adquisiciones</t>
-  </si>
-  <si>
-    <t>Arrendamientos</t>
-  </si>
-  <si>
-    <t>Servicios</t>
-  </si>
-  <si>
-    <t>Nacional</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Carretera</t>
-  </si>
-  <si>
-    <t>Privada</t>
-  </si>
-  <si>
-    <t>Eje vial</t>
-  </si>
-  <si>
-    <t>Circunvalación</t>
-  </si>
-  <si>
-    <t>Brecha</t>
-  </si>
-  <si>
-    <t>Diagonal</t>
-  </si>
-  <si>
-    <t>Calle</t>
-  </si>
-  <si>
-    <t>Corredor</t>
-  </si>
-  <si>
-    <t>Circuito</t>
-  </si>
-  <si>
-    <t>Pasaje</t>
-  </si>
-  <si>
-    <t>Vereda</t>
-  </si>
-  <si>
-    <t>Calzada</t>
-  </si>
-  <si>
-    <t>Viaducto</t>
-  </si>
-  <si>
-    <t>Prolongación</t>
-  </si>
-  <si>
-    <t>Boulevard</t>
-  </si>
-  <si>
-    <t>Peatonal</t>
-  </si>
-  <si>
-    <t>Retorno</t>
-  </si>
-  <si>
-    <t>Camino</t>
-  </si>
-  <si>
-    <t>Callejón</t>
-  </si>
-  <si>
-    <t>Cerrada</t>
-  </si>
-  <si>
-    <t>Ampliación</t>
-  </si>
-  <si>
-    <t>Continuación</t>
-  </si>
-  <si>
-    <t>Terracería</t>
-  </si>
-  <si>
-    <t>Andador</t>
-  </si>
-  <si>
-    <t>Periférico</t>
-  </si>
-  <si>
-    <t>Avenida</t>
-  </si>
-  <si>
-    <t>Aeropuerto</t>
-  </si>
-  <si>
-    <t>Barrio</t>
-  </si>
-  <si>
-    <t>Cantón</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Ciudad industrial</t>
-  </si>
-  <si>
-    <t>Colonia</t>
-  </si>
-  <si>
-    <t>Condominio</t>
-  </si>
-  <si>
-    <t>Conjunto habitacional</t>
-  </si>
-  <si>
-    <t>Corredor industrial</t>
-  </si>
-  <si>
-    <t>Coto</t>
-  </si>
-  <si>
-    <t>Cuartel</t>
-  </si>
-  <si>
-    <t>Ejido</t>
-  </si>
-  <si>
-    <t>Exhacienda</t>
-  </si>
-  <si>
-    <t>Fracción</t>
-  </si>
-  <si>
-    <t>Fraccionamiento</t>
-  </si>
-  <si>
-    <t>Granja</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
-    <t>Ingenio</t>
-  </si>
-  <si>
-    <t>Manzana</t>
-  </si>
-  <si>
-    <t>Paraje</t>
-  </si>
-  <si>
-    <t>Parque industrial</t>
-  </si>
-  <si>
-    <t>Pueblo</t>
-  </si>
-  <si>
-    <t>Puerto</t>
-  </si>
-  <si>
-    <t>Ranchería</t>
-  </si>
-  <si>
-    <t>Rancho</t>
-  </si>
-  <si>
-    <t>Región</t>
-  </si>
-  <si>
-    <t>Residencial</t>
-  </si>
-  <si>
-    <t>Rinconada</t>
-  </si>
-  <si>
-    <t>Sección</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Supermanzana</t>
-  </si>
-  <si>
-    <t>Unidad</t>
-  </si>
-  <si>
-    <t>Unidad habitacional</t>
-  </si>
-  <si>
-    <t>Villa</t>
-  </si>
-  <si>
-    <t>Zona federal</t>
-  </si>
-  <si>
-    <t>Zona industrial</t>
-  </si>
-  <si>
-    <t>Zona militar</t>
-  </si>
-  <si>
-    <t>Zona naval</t>
-  </si>
-  <si>
-    <t>México</t>
-  </si>
-  <si>
-    <t>Guerrero</t>
-  </si>
-  <si>
-    <t>Puebla</t>
-  </si>
-  <si>
-    <t>Quintana Roo</t>
-  </si>
-  <si>
-    <t>Guanajuato</t>
-  </si>
-  <si>
-    <t>Durango</t>
-  </si>
-  <si>
-    <t>Michoacán de Ocampo</t>
-  </si>
-  <si>
-    <t>San Luis Potosí</t>
-  </si>
-  <si>
-    <t>Campeche</t>
-  </si>
-  <si>
-    <t>Coahuila de Zaragoza</t>
-  </si>
-  <si>
-    <t>Nayarit</t>
-  </si>
-  <si>
-    <t>Zacatecas</t>
-  </si>
-  <si>
-    <t>Morelos</t>
-  </si>
-  <si>
-    <t>Sonora</t>
-  </si>
-  <si>
-    <t>Baja California Sur</t>
-  </si>
-  <si>
-    <t>Colima</t>
-  </si>
-  <si>
-    <t>Tabasco</t>
-  </si>
-  <si>
-    <t>Oaxaca</t>
-  </si>
-  <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
-    <t>Jalisco</t>
-  </si>
-  <si>
-    <t>Chiapas</t>
-  </si>
-  <si>
-    <t>Hidalgo</t>
-  </si>
-  <si>
-    <t>Aguascalientes</t>
-  </si>
-  <si>
-    <t>Tamaulipas</t>
-  </si>
-  <si>
-    <t>Sinaloa</t>
-  </si>
-  <si>
-    <t>Yucatán</t>
-  </si>
-  <si>
-    <t>Chihuahua</t>
-  </si>
-  <si>
-    <t>Querétaro</t>
-  </si>
-  <si>
-    <t>Nuevo León</t>
-  </si>
-  <si>
-    <t>Veracruz de Ignacio de la Llave</t>
-  </si>
-  <si>
-    <t>Ciudad de México</t>
-  </si>
-  <si>
-    <t>Baja California</t>
-  </si>
-  <si>
-    <t>Federales</t>
-  </si>
-  <si>
-    <t>Estatales</t>
-  </si>
-  <si>
-    <t>Municipales</t>
-  </si>
-  <si>
-    <t>En planeación</t>
-  </si>
-  <si>
-    <t>En ejecución</t>
-  </si>
-  <si>
-    <t>En finiquito</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>56475</t>
-  </si>
-  <si>
-    <t>56476</t>
-  </si>
-  <si>
-    <t>56477</t>
-  </si>
-  <si>
-    <t>56478</t>
-  </si>
-  <si>
-    <t>56479</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Nombre(s)</t>
-  </si>
-  <si>
-    <t>Primer apellido</t>
-  </si>
-  <si>
-    <t>Segundo apellido</t>
-  </si>
-  <si>
-    <t>Razón Social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFC de los posibles contratantes </t>
-  </si>
-  <si>
-    <t>7B98730475A8D6A1FBC89CCB4A30E6FB</t>
-  </si>
-  <si>
-    <t>4A5F7557AB7ED02B1FEEF40D373DFA80</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021C733456342BA0BC2</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021972DCE701F1E277B</t>
-  </si>
-  <si>
-    <t>115AB40B944E80BCB1ABD5C0E345140C</t>
-  </si>
-  <si>
-    <t>EAF8D02516F0D148EE5D8BCA970FEE57</t>
-  </si>
-  <si>
-    <t>4FB59ACACCC67CD5880367A1EAC78DDD</t>
-  </si>
-  <si>
-    <t>692D6519DEF82E17CF97162329412E40</t>
+    <t>AE57B1F2A7057647B7A30FE4846CD607</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E07F561E97CBDD8FF2F</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E0726EB72A9072CE7E1</t>
   </si>
   <si>
     <t>56480</t>
@@ -1044,6 +1051,9 @@
     <t>56483</t>
   </si>
   <si>
+    <t>77807</t>
+  </si>
+  <si>
     <t>56484</t>
   </si>
   <si>
@@ -1053,28 +1063,16 @@
     <t>RFC de las personas físicas o morales que presentaron una proposición u oferta</t>
   </si>
   <si>
-    <t>7B98730475A8D6A1097EF940ACFD486E</t>
-  </si>
-  <si>
-    <t>4A5F7557AB7ED02BE31A530828D9C3FC</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021B4A11A93A223062D</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021A64BB8E972EC65D7</t>
-  </si>
-  <si>
-    <t>EE4F75063C75F2FE6014909BC61DC2E7</t>
-  </si>
-  <si>
-    <t>78BA2A261A02E3C30F474F1A708BD6A0</t>
-  </si>
-  <si>
-    <t>05CFD7F60DBD7C965492056735BEBFB3</t>
-  </si>
-  <si>
-    <t>1E9F4B743D19310B9E339DE69F993085</t>
+    <t>AE57B1F2A7057647198C40CBFF5E7988</t>
+  </si>
+  <si>
+    <t>AE57B1F2A7057647210B96B69A7B68AE</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E0781340809ED168F78</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E07F96166D0A49F1136</t>
   </si>
   <si>
     <t>56485</t>
@@ -1089,25 +1087,25 @@
     <t>56488</t>
   </si>
   <si>
+    <t>77802</t>
+  </si>
+  <si>
     <t>56489</t>
   </si>
   <si>
     <t>RFC de las personas físicas o morales asistentes a la junta de aclaraciones</t>
   </si>
   <si>
-    <t>7B98730475A8D6A1235FBFE0671830C6</t>
-  </si>
-  <si>
-    <t>4A5F7557AB7ED02B7061FA6E207F85C0</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E80210F57777C27A1BFA2</t>
-  </si>
-  <si>
-    <t>F9F90E95EA1F85B79F83CC8BAE113F09</t>
-  </si>
-  <si>
-    <t>1E799E84951B2EBBFB6CE3A41E06CC2A</t>
+    <t>AE57B1F2A7057647C1EEA04A7B84C11B</t>
+  </si>
+  <si>
+    <t>AE57B1F2A7057647A47A3726C1A9769B</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E0756B1A2F240729683</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E07F9116FAE5A5C684E</t>
   </si>
   <si>
     <t>56490</t>
@@ -1119,6 +1117,9 @@
     <t>56492</t>
   </si>
   <si>
+    <t>77812</t>
+  </si>
+  <si>
     <t>56494</t>
   </si>
   <si>
@@ -1140,28 +1141,16 @@
     <t>Cargo que ocupa el Servidor Público dentro del SO</t>
   </si>
   <si>
-    <t>7B98730475A8D6A19CBFB1373D343587</t>
-  </si>
-  <si>
-    <t>4A5F7557AB7ED02B3209822C523A6668</t>
-  </si>
-  <si>
-    <t>E369E12C440D25112A9E19F168030C1A</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021DEAFB985B843B24C</t>
-  </si>
-  <si>
-    <t>F4496594926D3142DED081D3A2826FBB</t>
-  </si>
-  <si>
-    <t>8C6FCE2315990137A9389C2EB25EC487</t>
-  </si>
-  <si>
-    <t>DBFD073FA2E1723F564C1C8CDA69784C</t>
-  </si>
-  <si>
-    <t>B07092B07A061B31DDFB2A963D1E5C70</t>
+    <t>AE57B1F2A705764779B61816D980A4B3</t>
+  </si>
+  <si>
+    <t>8F6BD8FAA81ECEE165ACFF7501CB64B2</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E071AA4EF8DFBF8ECC6</t>
+  </si>
+  <si>
+    <t>0724DB38E7E5673A4A4BEFCB0C08057F</t>
   </si>
   <si>
     <t>56495</t>
@@ -1170,28 +1159,16 @@
     <t>Partida Presupuestal</t>
   </si>
   <si>
-    <t>7B98730475A8D6A1D9D88D3CDBEF9D3F</t>
-  </si>
-  <si>
-    <t>4A5F7557AB7ED02B204A2E785DF921DF</t>
-  </si>
-  <si>
-    <t>E369E12C440D2511387D4345E304680E</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E8021C760DDBDF124B1C4</t>
-  </si>
-  <si>
-    <t>D3EB352698542D66C6E555652C16E682</t>
-  </si>
-  <si>
-    <t>22983694B7B9B96623459D672DA910B4</t>
-  </si>
-  <si>
-    <t>3777BC5EEEFA274BA71FA0DB3C79E5C4</t>
-  </si>
-  <si>
-    <t>F2926595CB61A92BFC7C923111D7BDD5</t>
+    <t>AE57B1F2A7057647238907243E9A32CD</t>
+  </si>
+  <si>
+    <t>8F6BD8FAA81ECEE1860FD747DFA68EB9</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E07727D24755043F76B</t>
+  </si>
+  <si>
+    <t>0724DB38E7E5673A976AACB9BD92FFF7</t>
   </si>
   <si>
     <t>56496</t>
@@ -1218,28 +1195,16 @@
     <t>Hipervínculo al documento del convenio</t>
   </si>
   <si>
-    <t>7B98730475A8D6A1C429E074A855C50A</t>
-  </si>
-  <si>
-    <t>7B98730475A8D6A161E5625A5E6B43A3</t>
-  </si>
-  <si>
-    <t>E369E12C440D25117C33D3C82E753F59</t>
-  </si>
-  <si>
-    <t>0FFB87ECF09E80216339309DA67C2825</t>
-  </si>
-  <si>
-    <t>BD4D75C53BED8C4206860CE43400D646</t>
-  </si>
-  <si>
-    <t>FDBFB60596F45444C9939671CC26F8B2</t>
-  </si>
-  <si>
-    <t>6493AF102EEC7F1C0F229151D03B420A</t>
-  </si>
-  <si>
-    <t>F6C99739233827DB8207D228765A582B</t>
+    <t>AE57B1F2A7057647CBE5A1FF3D0F6DD6</t>
+  </si>
+  <si>
+    <t>8F6BD8FAA81ECEE1705D09DFBF7694FE</t>
+  </si>
+  <si>
+    <t>7DE8CFD837056E07935E65299B6D6C98</t>
+  </si>
+  <si>
+    <t>0724DB38E7E5673A1A1585CB788C3E87</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CC9"/>
+  <dimension ref="A1:CD9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
@@ -1661,72 +1626,73 @@
     <col min="21" max="21" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="69.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="61" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="74.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="69" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="66.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="64.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="77.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="73" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="84" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="60" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="60.85546875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="50.42578125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="44" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="68.28515625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="82" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="51.140625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="57" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="51.5703125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="76.5703125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="82" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="20" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="255" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="61" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="69" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="77.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="73" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="84" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="60" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="62.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="44" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="82" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="57" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="82" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="20" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1743,7 +1709,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1758,7 +1724,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1826,13 +1792,13 @@
         <v>11</v>
       </c>
       <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>8</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>6</v>
       </c>
       <c r="AA4" t="s">
         <v>6</v>
@@ -1841,34 +1807,34 @@
         <v>6</v>
       </c>
       <c r="AC4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD4" t="s">
         <v>8</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>11</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>11</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>6</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>11</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>6</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>8</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>6</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>11</v>
       </c>
       <c r="AM4" t="s">
         <v>11</v>
@@ -1892,10 +1858,10 @@
         <v>11</v>
       </c>
       <c r="AT4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU4" t="s">
         <v>6</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>7</v>
       </c>
       <c r="AV4" t="s">
         <v>7</v>
@@ -1904,7 +1870,7 @@
         <v>7</v>
       </c>
       <c r="AX4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="s">
         <v>12</v>
@@ -1916,7 +1882,7 @@
         <v>12</v>
       </c>
       <c r="BB4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="s">
         <v>6</v>
@@ -1925,58 +1891,58 @@
         <v>6</v>
       </c>
       <c r="BE4" t="s">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="s">
         <v>11</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>7</v>
       </c>
       <c r="BG4" t="s">
         <v>7</v>
       </c>
       <c r="BH4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BI4" t="s">
         <v>10</v>
       </c>
       <c r="BJ4" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK4" t="s">
         <v>9</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>8</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>6</v>
       </c>
       <c r="BM4" t="s">
         <v>6</v>
       </c>
       <c r="BN4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="s">
         <v>11</v>
       </c>
       <c r="BP4" t="s">
+        <v>11</v>
+      </c>
+      <c r="BQ4" t="s">
         <v>10</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BR4" t="s">
         <v>11</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>8</v>
       </c>
       <c r="BS4" t="s">
         <v>8</v>
       </c>
       <c r="BT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="s">
         <v>9</v>
       </c>
-      <c r="BU4" t="s">
+      <c r="BV4" t="s">
         <v>11</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>10</v>
       </c>
       <c r="BW4" t="s">
         <v>10</v>
@@ -1988,19 +1954,22 @@
         <v>10</v>
       </c>
       <c r="BZ4" t="s">
+        <v>10</v>
+      </c>
+      <c r="CA4" t="s">
         <v>11</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CB4" t="s">
         <v>7</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CC4" t="s">
         <v>13</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CD4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:81" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:82" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -2241,10 +2210,13 @@
       <c r="CC5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="6" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2326,742 +2298,752 @@
       <c r="CA6" s="5"/>
       <c r="CB6" s="5"/>
       <c r="CC6" s="5"/>
-    </row>
-    <row r="7" spans="1:81" ht="39" x14ac:dyDescent="0.25">
+      <c r="CD6" s="5"/>
+    </row>
+    <row r="7" spans="1:82" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP7" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ7" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR7" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS7" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT7" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV7" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY7" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ7" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB7" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC7" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD7" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE7" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG7" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH7" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK7" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL7" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN7" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO7" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP7" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ7" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR7" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS7" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT7" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU7" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV7" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW7" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX7" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY7" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ7" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA7" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB7" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC7" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:81" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="CD7" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="X8" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="Y8" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AQ8" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AS8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AT8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AU8" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AV8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AW8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AZ8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BA8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BB8" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BC8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BD8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BE8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BF8" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BG8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BH8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BI8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BJ8" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="BK8" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="BL8" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BM8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BN8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BO8" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BP8" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BQ8" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BR8" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BS8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BT8" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="BU8" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BV8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BX8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BY8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ8" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="CA8" s="3" t="s">
         <v>189</v>
       </c>
       <c r="CB8" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CC8" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="9" spans="1:81" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CD8" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:82" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AP9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AQ9" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AS9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AT9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AU9" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AV9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AW9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AZ9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BA9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BB9" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BC9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BD9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BE9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BF9" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BG9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BH9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BI9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BJ9" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="BK9" s="3" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="BL9" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BM9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BN9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BO9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BP9" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BQ9" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BR9" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="BS9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BT9" s="3" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="BU9" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="BV9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BX9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BY9" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ9" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="CA9" s="3" t="s">
         <v>189</v>
       </c>
       <c r="CB9" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CC9" s="3" t="s">
         <v>190</v>
       </c>
+      <c r="CD9" s="3" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:CC6"/>
+    <mergeCell ref="A6:CD6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -3069,33 +3051,36 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F199">
       <formula1>Hidden_25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G199">
       <formula1>Hidden_36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y195">
-      <formula1>Hidden_424</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X199">
+      <formula1>Hidden_423</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC8:AC195">
-      <formula1>Hidden_528</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z199">
+      <formula1>Hidden_525</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AJ8:AJ195">
-      <formula1>Hidden_635</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD8:AD199">
+      <formula1>Hidden_629</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BK8:BK195">
-      <formula1>Hidden_762</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK8:AK199">
+      <formula1>Hidden_736</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BR8:BR195">
-      <formula1>Hidden_869</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BL8:BL199">
+      <formula1>Hidden_863</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BS8:BS195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BS8:BS199">
       <formula1>Hidden_970</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BT8:BT199">
+      <formula1>Hidden_1071</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3104,17 +3089,22 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3124,255 +3114,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>179</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3382,19 +3134,20 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="84" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -3408,239 +3161,406 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="G2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="H2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>204</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
+      <formula1>Hidden_1_Tabla_4364446</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="84" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
+      <formula1>Hidden_1_Tabla_4364736</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -3649,10 +3569,11 @@
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="78.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="78.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -3666,160 +3587,183 @@
         <v>11</v>
       </c>
       <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G2" t="s">
         <v>343</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>344</v>
       </c>
-      <c r="E2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>333</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
+      <formula1>Hidden_1_Tabla_4364746</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3827,21 +3771,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -3852,578 +3797,186 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G2" t="s">
         <v>354</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>355</v>
       </c>
-      <c r="E2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>182</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>182</v>
+        <v>323</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>182</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4364755</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>177</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4438,17 +3991,239 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4463,27 +4238,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4498,12 +4273,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4513,137 +4288,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4653,212 +4308,137 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4868,167 +4448,212 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>300</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -5038,22 +4663,167 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5068,17 +4838,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
